--- a/010-npm_node/02-results/2108OTH02RS Carina-Westland Revision.xlsx
+++ b/010-npm_node/02-results/2108OTH02RS Carina-Westland Revision.xlsx
@@ -464,7 +464,7 @@
         <v>CONTACT</v>
       </c>
       <c r="I2" t="str">
-        <v>CONTRACT_NUMBER</v>
+        <v>CONTRACT</v>
       </c>
       <c r="J2" t="str">
         <v>REVISIONS</v>
